--- a/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{036841BB-FE17-4F3A-8ADC-9E3207EE003B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27AAAD4E-55C7-4A65-8BBA-20579FD4EB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27AAAD4E-55C7-4A65-8BBA-20579FD4EB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F2E306D-6ABF-4103-A5F0-EF917665C66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F2E306D-6ABF-4103-A5F0-EF917665C66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64B1ABC9-724C-4066-98B1-B64D22B47330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NZL/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64B1ABC9-724C-4066-98B1-B64D22B47330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2080949-AA2C-40E6-8C0C-768B5EE51BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="93">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -358,6 +384,9 @@
   </si>
   <si>
     <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -972,15 +1001,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.57943469536758585</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -1012,7 +1038,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1261,7 +1287,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3">
         <v>0.24174053182916999</v>
@@ -1611,12 +1637,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -1645,7 +1671,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <v>1.5</v>
@@ -1966,7 +1992,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2092,7 +2118,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2218,7 +2244,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2344,7 +2370,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2470,7 +2496,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2596,7 +2622,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2722,7 +2748,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2848,7 +2874,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -2974,7 +3000,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3100,7 +3126,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3226,7 +3252,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3352,7 +3378,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3478,7 +3504,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3604,7 +3630,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3730,7 +3756,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3856,7 +3882,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -3982,7 +4008,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4108,7 +4134,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4234,7 +4260,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4360,7 +4386,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4486,7 +4512,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4612,7 +4638,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4738,7 +4764,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4864,7 +4890,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -4984,7 +5010,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5104,7 +5130,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5224,7 +5250,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5344,7 +5370,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5464,7 +5490,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5584,7 +5610,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5704,7 +5730,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5824,7 +5850,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -5944,7 +5970,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6064,7 +6090,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6184,7 +6210,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6304,7 +6330,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6424,7 +6450,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6544,7 +6570,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6664,7 +6690,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6784,7 +6810,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -6904,7 +6930,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7024,7 +7050,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7144,7 +7170,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7264,7 +7290,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7384,7 +7410,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7504,7 +7530,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7624,7 +7650,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7744,7 +7770,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -7870,7 +7896,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -7996,7 +8022,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8122,7 +8148,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8248,7 +8274,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8374,7 +8400,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8500,7 +8526,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8626,7 +8652,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8752,7 +8778,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -8878,7 +8904,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9004,7 +9030,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9130,7 +9156,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9256,7 +9282,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9382,7 +9408,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9508,7 +9534,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9634,7 +9660,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9760,7 +9786,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -9886,7 +9912,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10012,7 +10038,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10138,7 +10164,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10264,7 +10290,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10390,7 +10416,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10516,7 +10542,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10642,7 +10668,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10768,7 +10794,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B649">
         <v>2023</v>
